--- a/GameConfig/Datas/glass.xlsx
+++ b/GameConfig/Datas/glass.xlsx
@@ -2,18 +2,103 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49c9d781e33a4d70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R57f3342ddc484041"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:si>
+    <x:t xml:space="preserve">##var</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">id</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kind</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">maxDurability</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">hitDurabilityLoss</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">prefabLocation</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">stageUpperRatios</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">stageSprites</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##type</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">int</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">string</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(array#sep=;),float</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">(array#sep=;),string</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##group</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">c</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">##</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">玻璃ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">种类：0 Normal，1 Colored</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">最大耐久</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">每次命中耐久损失</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Prefab资源地址</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">阶段耐久比上限</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">阶段图片资源地址</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GlassNormal</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">0.34;0.67;1</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GlassNormalHeavy;GlassNormalLight;GlassNormalIntact</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GlassColored</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">GlassColoredHeavy;GlassColoredLight;GlassColoredIntact</x:t>
+  </x:si>
+</x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="2">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -21,6 +106,20 @@
     <x:font>
       <x:sz val="11"/>
       <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="9"/>
+      <x:name val="宋体"/>
+      <x:family val="3"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Arial"/>
+      <x:family val="2"/>
     </x:font>
   </x:fonts>
   <x:fills count="4">
@@ -42,19 +141,28 @@
     </x:fill>
   </x:fills>
   <x:borders count="1">
-    <x:border/>
+    <x:border>
+      <x:left/>
+      <x:right/>
+      <x:top/>
+      <x:bottom/>
+      <x:diagonal/>
+    </x:border>
   </x:borders>
-  <x:cellStyleXfs count="1">
+  <x:cellStyleXfs count="2">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="5">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </x:cellXfs>
-  <x:cellStyles count="1">
-    <x:cellStyle name="Normal" xfId="0"/>
+  <x:cellStyles count="2">
+    <x:cellStyle name="Normal" xfId="1"/>
+    <x:cellStyle name="常规" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
 </file>
@@ -254,45 +362,44 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="30" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="78" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10" customWidth="1"/>
+    <x:col min="2" max="2" width="16" customWidth="1"/>
+    <x:col min="3" max="3" width="26" customWidth="1"/>
+    <x:col min="4" max="4" width="22" customWidth="1"/>
+    <x:col min="5" max="6" width="24" customWidth="1"/>
+    <x:col min="7" max="7" width="30" customWidth="1"/>
+    <x:col min="8" max="8" width="78" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="2" t="str">
-        <x:v>##var</x:v>
-      </x:c>
-      <x:c r="B1" s="2" t="str">
-        <x:v>id</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="str">
-        <x:v>kind</x:v>
-      </x:c>
-      <x:c r="D1" s="2" t="str">
-        <x:v>maxDurability</x:v>
-      </x:c>
-      <x:c r="E1" s="2" t="str">
-        <x:v>hitDurabilityLoss</x:v>
-      </x:c>
-      <x:c r="F1" s="2" t="str">
-        <x:v>prefabLocation</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="str">
-        <x:v>stageUpperRatios</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="str">
-        <x:v>stageSprites</x:v>
+      <x:c r="A1" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E1" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="1" t="str">
-        <x:v>##var</x:v>
+      <x:c r="A2" s="1" t="s">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -303,129 +410,129 @@
       <x:c r="H2" s="1"/>
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
-      <x:c r="A3" s="1" t="str">
-        <x:v>##type</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="E3" s="1" t="str">
-        <x:v>int</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="G3" s="1" t="str">
-        <x:v>(array#sep=;),float</x:v>
-      </x:c>
-      <x:c r="H3" s="1" t="str">
-        <x:v>(array#sep=;),string</x:v>
+      <x:c r="A3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H3" s="1" t="s">
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
-      <x:c r="A4" s="1" t="str">
-        <x:v>##group</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="D4" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="E4" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="G4" s="1" t="str">
-        <x:v>c</x:v>
-      </x:c>
-      <x:c r="H4" s="1" t="str">
-        <x:v>c</x:v>
+      <x:c r="A4" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G4" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="H4" s="1" t="s">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
-      <x:c r="A5" s="3" t="str">
-        <x:v>##</x:v>
-      </x:c>
-      <x:c r="B5" s="3" t="str">
-        <x:v>玻璃ID</x:v>
-      </x:c>
-      <x:c r="C5" s="3" t="str">
-        <x:v>种类：0 Normal，1 Colored</x:v>
-      </x:c>
-      <x:c r="D5" s="3" t="str">
-        <x:v>最大耐久</x:v>
-      </x:c>
-      <x:c r="E5" s="3" t="str">
-        <x:v>每次命中耐久损失</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="str">
-        <x:v>Prefab资源地址</x:v>
-      </x:c>
-      <x:c r="G5" s="3" t="str">
-        <x:v>阶段耐久比上限</x:v>
-      </x:c>
-      <x:c r="H5" s="3" t="str">
-        <x:v>阶段图片资源地址</x:v>
+      <x:c r="A5" s="3" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B5" s="3" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C5" s="3" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D5" s="3" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="E5" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F5" s="3" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G5" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="1"/>
-      <x:c r="B6" s="1" t="n">
+      <x:c r="B6" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="n">
+      <x:c r="C6" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D6" s="1" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E6" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F6" s="1" t="str">
-        <x:v>GlassNormal</x:v>
-      </x:c>
-      <x:c r="G6" s="1" t="str">
-        <x:v>0.34;0.67;1</x:v>
-      </x:c>
-      <x:c r="H6" s="1" t="str">
-        <x:v>GlassNormalHeavy;GlassNormalLight;GlassNormalIntact</x:v>
+      <x:c r="F6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H6" s="1" t="s">
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="1"/>
-      <x:c r="B7" s="1" t="n">
+      <x:c r="B7" s="1">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C7" s="1" t="n">
+      <x:c r="C7" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D7" s="1" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E7" s="1">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F7" s="1" t="str">
-        <x:v>GlassColored</x:v>
-      </x:c>
-      <x:c r="G7" s="1" t="str">
-        <x:v>0.34;0.67;1</x:v>
-      </x:c>
-      <x:c r="H7" s="1" t="str">
-        <x:v>GlassColoredHeavy;GlassColoredLight;GlassColoredIntact</x:v>
+      <x:c r="F7" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G7" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H7" s="1" t="s">
+        <x:v>27</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
